--- a/테스트/테스트3차/5회/문채아/테스트시나리오_문채아.xlsx
+++ b/테스트/테스트3차/5회/문채아/테스트시나리오_문채아.xlsx
@@ -3891,7 +3891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4081,17 +4081,17 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>비뇨기과·재활의학과·정형외과·신경과 또는 신경외과 넷뿐 — 비뇨기과로 넣었다</t>
+          <t>비뇨기과·재활의학과·정형외과·신경과 또는 신경외과 넷뿐 — 비뇨기과로 넣어야 했다</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>소아 환자가 다섯인 회차라 눈에 띈다. 마스터에 소아비뇨의학과를 더할지 확인 필요</t>
+          <t>목록에 없어 바꿔 적으면 과목별로 셀 때 소아 건이 보이지 않는다. 여덟 사람 가운데 다섯이 미성년인 회차다. 「소아비뇨의학과」를 더하고 배포 (OrderReason::SPECIALTIES). 요청서 12쪽이 정한 목록에 한 줄을 더한 것이라 담당자 확인이 필요하다</t>
         </is>
       </c>
       <c r="J3" s="55" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>조치완료</t>
         </is>
       </c>
       <c r="K3" s="55" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="L3" s="55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="M3" s="55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발팀</t>
         </is>
       </c>
     </row>
@@ -4133,32 +4133,32 @@
       </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>처방외 건은 상세 목록을 저장해도 문자가 한 통도 발송되지 않음</t>
+          <t>처방전 접수 안내가 못 나간 까닭을 화면이 말하지 않는다</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
-          <t>유형 [처방외] 선택 후 상세 목록 저장 → 메시지 관리 확인</t>
+          <t>거래처 연락처가 빈 상태에서 상세 목록 저장</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>적어도 접수 안내 SMS 는 발송</t>
+          <t>「연락처가 없어 접수 안내를 보내지 못했습니다」 안내</t>
         </is>
       </c>
       <c r="H4" s="15" t="inlineStr">
         <is>
-          <t>접수 안내·위임동의 모두 미발송 (앞의 다섯 사람은 2건 발송)</t>
+          <t>아무 말도 없음 — 이미 보낸 것과 구별되지 않는다</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr">
         <is>
-          <t>위임동의를 보내지 않는 것은 의도된 동작(공단에 청구할 것이 없어 「위임 해당 없음」). 그러나 접수 안내까지 나가지 않는 것은 뜻이 없어 보인다 — 처방외라도 주문은 접수됐고 환자는 그것을 알아야 한다. 확인 필요</t>
+          <t>위임동의는 못 보낸 까닭을 말하는데 접수 안내는 참·거짓만 돌려주고 있었다. 담당자는 나간 줄 알고 기다린다. 까닭을 함께 돌려주고 화면이 못 나간 것만 적도록 수정하고 배포 (PrescriptionController · order.blade.php). 3차 5회 문채아에서 문자 2통이 모두 안 나가 드러났다 — 그 건의 직접 원인은 수행자가 연락처를 넣지 못한 것이며 처방외 갈래와는 무관하다</t>
         </is>
       </c>
       <c r="J4" s="52" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>조치완료</t>
         </is>
       </c>
       <c r="K4" s="52" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="L4" s="52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="M4" s="52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발팀</t>
         </is>
       </c>
     </row>
@@ -4185,47 +4185,47 @@
       </c>
       <c r="B5" s="55" t="inlineStr">
         <is>
-          <t>TC-011</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>TC-008</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>중대</t>
         </is>
       </c>
       <c r="D5" s="55" t="inlineStr">
         <is>
-          <t>사용성</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>처방외 건은 개인정보 동의를 받을 길이 잘 보이지 않는다</t>
+          <t>한 번 들어간 자격을 화면에서 비울 수 없다</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>처방외 건에서 머리띠의 위임동의 단추와 [개인정보동의] 팝오버 확인</t>
+          <t>자격이 들어간 건에서 자격을 [선택]으로 되돌려 저장 → 새로고침</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>개인정보 동의를 받는 길이 분명히 보인다</t>
+          <t>자격이 비워진다</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>머리띠에 「위임 해당 없음」이 붙어 담당자가 건너뛰기 쉽다. [개인정보동의] 팝오버의 [위임동의 발송]을 눌러야 보낼 수 있다</t>
+          <t>그대로 남는다 (여러 번 시도해도 같다)</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>보낼 수는 있다(단추가 잠겨 있지 않고 눌러 보니 실제로 발송됨). 다만 「위임 해당 없음」만 보고 개인정보 동의까지 건너뛸 수 있다. 처방외 건에는 「개인정보 동의만 받는 링크」를 따로 두거나 「위임 해당 없음」 옆에 「개인정보 동의는 받아야 합니다」를 적어 주는 편이 낫다. 확인 필요</t>
+          <t>저장 거르개가 fn ($v) =&gt; $v !== null 인데 라라벨이 빈 문자열을 null 로 바꾸므로(ConvertEmptyStringsToNull) 비우려고 보낸 것도 함께 걸렸다. 자격은 화면이 그 이름으로 보내 왔을 때만 비우도록 따로 받고, 비우면 청구전략 열쇠도 다시 셈하도록 수정하고 배포. 운영에서 「일반 → (빔)」 확인. 같은 거르개를 쓰는 다른 칸도 같은 성질을 가지므로 어디까지 비울 수 있어야 하는지는 담당자 판단이 필요하다</t>
         </is>
       </c>
       <c r="J5" s="55" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>조치완료</t>
         </is>
       </c>
       <c r="K5" s="55" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="L5" s="55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="M5" s="55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발팀</t>
         </is>
       </c>
     </row>
@@ -4252,47 +4252,47 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="C6" s="57" t="inlineStr">
-        <is>
-          <t>경미</t>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>사용성</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>서명 화면의 보험 선택지에 「처방외」가 없다</t>
+          <t>「위임 해당 없음」만 보고 개인정보 동의를 건너뛰기 쉽다</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
         <is>
-          <t>처방외 건의 위임동의 서명 화면에서 보험 항목 확인</t>
+          <t>처방외·산재·자동차보험 건에서 머리띠 확인</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>처방외에 맞는 선택지</t>
+          <t>개인정보 동의가 남았다는 것이 보인다</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>일반·보훈·산업재해·자동차보험 넷뿐 — 「일반」을 고를 수밖에 없다</t>
+          <t>「위임 해당 없음」 한 줄뿐 — 위임이 없으니 아무것도 안 받아도 되는 것으로 읽힌다</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>처방외는 보험 자체가 없는 갈래인데 화면이 그것을 말할 수 없다. 「해당 없음」이나 「비급여(처방외)」를 더하는 편이 낫다. 이 선택이 목록의 자격 칸에까지 넘어간다</t>
+          <t>딱지 아래에 「개인정보 동의는 받습니다」를 붙이고, 말풍선에 「같은 링크로 함께 받습니다」를 적었다. 받아 둔 뒤에는 그 줄만 물러난다. 배포 완료 (order.blade.php)</t>
         </is>
       </c>
       <c r="J6" s="52" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>조치완료</t>
         </is>
       </c>
       <c r="K6" s="52" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="L6" s="52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="M6" s="52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발팀</t>
         </is>
       </c>
     </row>
@@ -4319,42 +4319,42 @@
       </c>
       <c r="B7" s="55" t="inlineStr">
         <is>
-          <t>TC-012</t>
-        </is>
-      </c>
-      <c r="C7" s="58" t="inlineStr">
-        <is>
-          <t>정보</t>
+          <t>TC-011</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>경미</t>
         </is>
       </c>
       <c r="D7" s="55" t="inlineStr">
         <is>
-          <t>수행</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>서명 캔버스가 전체화면 캡처 후 초기화됨</t>
+          <t>문자와 서명 화면의 이름에 (E) 접두가 빠진다</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>서명 입력 → 전체화면(fullPage) 캡처 → 동의 서명 클릭</t>
+          <t>위임동의 발송 → 문자 본문과 서명 화면의 이름 확인</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>서명이 유지된 상태로 제출</t>
+          <t>거래처 이름과 같은 「(E)(T3-5)문채아」</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>「서명이 비어 있습니다」로 차단</t>
+          <t>「(T3-5)문채아」 — 앞의 강도원은 (E) 가 붙어 나왔다</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>서명은 화면에 보이는 상태에서 입력하고, 잉크 유무를 확인한 뒤 제출. 캡처는 제출 전 일반 캡처로 수행</t>
+          <t>처방전에 적힌 이름을 쓰는 자리와 거래처 이름을 쓰는 자리가 갈리는 것으로 보인다. 일은 막히지 않으나 환자가 받는 문자에 다른 이름이 적힌다 — 확인 필요</t>
         </is>
       </c>
       <c r="J7" s="55" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="K7" s="55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L7" s="55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="55" t="inlineStr">
@@ -4386,62 +4386,62 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>TC-013</t>
-        </is>
-      </c>
-      <c r="C8" s="53" t="inlineStr">
-        <is>
-          <t>정보</t>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="C8" s="57" t="inlineStr">
+        <is>
+          <t>경미</t>
         </is>
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>환경</t>
+          <t>기능</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>동의 완료 시 공단 등록 서류 팩스가 자동 발송되지 않음</t>
+          <t>서명 화면의 보험 선택지에 「처방외」가 없다</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>위임동의 서명 완료 → 발송 이력 확인</t>
+          <t>처방외 건의 위임동의 서명 화면에서 보험 항목 확인</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>설정에 따라 자동 발송</t>
+          <t>처방외에 맞는 선택지</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>자동 발송되지 않음</t>
+          <t>일반·보훈·산업재해·자동차보험 넷뿐 — 「일반」을 고를 수밖에 없다</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr">
         <is>
-          <t>[동의 완료에 공단 팩스 발송] 설정이 꺼져 있는 상태. 설정값대로 동작한 것이며 결함 아님. TC-013a 수동 발송으로 진행</t>
+          <t>「해당 없음(처방외)」을 더하고 배포 (consent/sign.blade.php). 확인은 다음 사람 서명 화면에서 한다 — 문채아 건은 이미 동의를 마쳐 링크가 완료 화면으로 바뀌었다</t>
         </is>
       </c>
       <c r="J8" s="52" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>조치완료</t>
         </is>
       </c>
       <c r="K8" s="52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L8" s="52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="M8" s="52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발팀</t>
         </is>
       </c>
     </row>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="B9" s="55" t="inlineStr">
         <is>
-          <t>TC-018</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>경미</t>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="D9" s="55" t="inlineStr">
@@ -4468,47 +4468,47 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>위드웍스 판매주문 확정자 칸이 비어 있음</t>
+          <t>처방외 건인데 서명 화면에서 고른 보험이 자격 칸으로 넘어온다</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>입금 확인(주문 확정) → 위드웍스 판매 주문 상세 목록 확인</t>
+          <t>처방외 건에서 자격을 비운 채 서명 → 주문 관리 목록의 자격 칸 확인</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>확정을 수행한 주체가 남는다</t>
+          <t>비어 있거나 「해당 없음」</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>확정자 칸이 빈 상태 (판매상태·확정판매금액·확정일자는 정상)</t>
+          <t>「일반」 — 서명 화면의 보험·지원자격이 그대로 옮겨 적힌다</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>so_confirm API 로 확정하면 화면 사용자가 없어 확정자가 남지 않음. 누가 확정했는지 추적하려면 연동 계정명을 남기도록 위드웍스 쪽 보완 필요 — CE Admin 활동 기록에는 남으므로 급하지 않음</t>
+          <t>ConsentController 가 「자격이 비어 있으면 서명 화면에서 읽어 채운다」로 되어 있었다. 처방외는 자격이 없는 갈래이므로 채우지 않도록 수정하고 배포</t>
         </is>
       </c>
       <c r="J9" s="55" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>조치완료</t>
         </is>
       </c>
       <c r="K9" s="55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="L9" s="55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="M9" s="55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발팀</t>
         </is>
       </c>
     </row>
@@ -4520,42 +4520,42 @@
       </c>
       <c r="B10" s="52" t="inlineStr">
         <is>
-          <t>TC-021</t>
-        </is>
-      </c>
-      <c r="C10" s="57" t="inlineStr">
-        <is>
-          <t>경미</t>
+          <t>TC-012</t>
+        </is>
+      </c>
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>정보</t>
         </is>
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>기능</t>
+          <t>수행</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>처방외 건의 청구 전략 코드가 「20|」로 끝난다</t>
+          <t>서명 캔버스가 전체화면 캡처 후 초기화됨</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>주문 관리 목록의 청구 전략 코드 칸 확인</t>
+          <t>서명 입력 → 전체화면(fullPage) 캡처 → 동의 서명 클릭</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>「20|처방외」 또는 「20」</t>
+          <t>서명이 유지된 상태로 제출</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>「20|」 — 파이프 뒤가 비어 있음</t>
+          <t>「서명이 비어 있습니다」로 차단</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>다른 건은 「10|산재」처럼 뒤에 자격이 붙는다. 처방외는 자격이 없으니 빈 것이 맞을 수 있으나 파이프로 끝나는 꼴은 자료로 넘길 때 헷갈린다. 확인 필요</t>
+          <t>서명은 화면에 보이는 상태에서 입력하고, 잉크 유무를 확인한 뒤 제출. 캡처는 제출 전 일반 캡처로 수행</t>
         </is>
       </c>
       <c r="J10" s="52" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="K10" s="52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="L10" s="52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="M10" s="52" t="inlineStr">
@@ -4587,62 +4587,196 @@
       </c>
       <c r="B11" s="55" t="inlineStr">
         <is>
+          <t>TC-013</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>정보</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>환경</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>동의 완료 시 공단 등록 서류 팩스가 자동 발송되지 않음</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>위임동의 서명 완료 → 발송 이력 확인</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>설정에 따라 자동 발송</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>자동 발송되지 않음</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>[동의 완료에 공단 팩스 발송] 설정이 꺼져 있는 상태. 설정값대로 동작한 것이며 결함 아님. TC-013a 수동 발송으로 진행</t>
+        </is>
+      </c>
+      <c r="J11" s="55" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="K11" s="55" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="L11" s="55" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="M11" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>OBS-11</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>TC-018</t>
+        </is>
+      </c>
+      <c r="C12" s="57" t="inlineStr">
+        <is>
+          <t>경미</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>위드웍스 판매주문 확정자 칸이 비어 있음</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>입금 확인(주문 확정) → 위드웍스 판매 주문 상세 목록 확인</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>확정을 수행한 주체가 남는다</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>확정자 칸이 빈 상태 (판매상태·확정판매금액·확정일자는 정상)</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>so_confirm API 로 확정하면 화면 사용자가 없어 확정자가 남지 않음. 누가 확정했는지 추적하려면 연동 계정명을 남기도록 위드웍스 쪽 보완 필요 — CE Admin 활동 기록에는 남으므로 급하지 않음</t>
+        </is>
+      </c>
+      <c r="J12" s="52" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+      <c r="K12" s="52" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="L12" s="52" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="M12" s="52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t>OBS-12</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
           <t>TC-021</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>경미</t>
         </is>
       </c>
-      <c r="D11" s="55" t="inlineStr">
+      <c r="D13" s="55" t="inlineStr">
         <is>
           <t>기능</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>자격을 고르지 않았는데 목록의 자격이 「일반」으로 표시됨</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>처방외 건에서 자격을 비운 채 진행 → 주문 관리 목록의 자격 칸 확인</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>비어 있거나 「해당 없음」</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>「일반」 — 서명 화면에서 고른 보험이 넘어온 것으로 보인다</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>위 「서명 화면에 처방외 선택지가 없다」의 결과다. 처방외 건의 자격은 비워 두거나 「해당 없음」이 맞다. 확인 필요</t>
-        </is>
-      </c>
-      <c r="J11" s="55" t="inlineStr">
-        <is>
-          <t>확인</t>
-        </is>
-      </c>
-      <c r="K11" s="55" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>처방외 건의 청구 전략 코드가 「20|」로 끝난다</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>주문 관리 목록의 청구 전략 코드 칸 확인</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>「20」</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>「20|」 — 파이프 뒤가 비어 있음</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>대조에 쓰는 열쇠 자체는 그대로 두고(저장된 값이라 바꾸면 위험하다) 표에 보일 때만 빈 꼬리를 떼도록 수정하고 배포 (OrderGridExtras). 운영에서 「20」 확인</t>
+        </is>
+      </c>
+      <c r="J13" s="55" t="inlineStr">
+        <is>
+          <t>조치완료</t>
+        </is>
+      </c>
+      <c r="K13" s="55" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="L11" s="55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M11" s="55" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="L13" s="55" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="M13" s="55" t="inlineStr">
+        <is>
+          <t>개발팀</t>
         </is>
       </c>
     </row>
